--- a/data/trans_bre/IP24_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP24_R-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 10,51</t>
+          <t>-14,46; 9,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 18,15</t>
+          <t>-9,26; 18,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 10,22</t>
+          <t>-9,93; 11,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 13,31</t>
+          <t>-13,38; 13,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-51,39; 70,57</t>
+          <t>-53,02; 62,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,51; 119,03</t>
+          <t>-35,03; 118,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-53,38; 120,43</t>
+          <t>-49,82; 125,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,4; 21,49</t>
+          <t>-18,01; 22,19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 18,02</t>
+          <t>0,77; 17,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 10,17</t>
+          <t>-6,05; 10,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 18,32</t>
+          <t>0,05; 17,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 57,94</t>
+          <t>2,48; 53,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 187,38</t>
+          <t>2,08; 179,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,49; 75,79</t>
+          <t>-30,55; 83,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 149,09</t>
+          <t>-0,02; 143,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,29; 636,84</t>
+          <t>14,07; 654,7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 22,76</t>
+          <t>-1,6; 22,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 11,93</t>
+          <t>-8,62; 10,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 17,25</t>
+          <t>-5,05; 17,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 9,9</t>
+          <t>-7,05; 9,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 145,72</t>
+          <t>-5,37; 148,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,16; 115,51</t>
+          <t>-46,76; 101,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-25,4; 134,65</t>
+          <t>-23,22; 125,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-52,41; 152,64</t>
+          <t>-52,74; 144,99</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 11,85</t>
+          <t>-8,29; 11,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 15,08</t>
+          <t>0,28; 15,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 22,03</t>
+          <t>0,07; 21,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,3; 6,99</t>
+          <t>-39,91; 6,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,97; 92,35</t>
+          <t>-37,34; 95,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 431,31</t>
+          <t>-10,31; 416,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 182,01</t>
+          <t>-0,54; 172,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,52; 79,94</t>
+          <t>-82,62; 68,78</t>
         </is>
       </c>
     </row>
@@ -1060,37 +1060,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 23,3</t>
+          <t>-10,7; 22,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 15,04</t>
+          <t>-11,18; 14,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 9,45</t>
+          <t>-13,8; 9,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 0,0</t>
+          <t>-7,74; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,7; 74,95</t>
+          <t>-23,18; 73,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-47,73; 184,38</t>
+          <t>-54,9; 165,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-77,71; 140,14</t>
+          <t>-78,82; 135,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,49 +1160,49 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 10,74</t>
+          <t>-11,62; 12,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 9,71</t>
+          <t>-13,96; 9,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 9,82</t>
+          <t>-9,62; 8,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 9,81</t>
+          <t>-13,31; 9,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-44,27; 59,64</t>
+          <t>-41,51; 74,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-57,81; 88,2</t>
+          <t>-58,14; 88,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-66,69; 166,88</t>
+          <t>-65,97; 177,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,21; 66,29</t>
+          <t>-55,54; 66,62</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 2,4</t>
+          <t>-15,09; 2,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 10,87</t>
+          <t>-4,75; 11,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 10,48</t>
+          <t>-5,08; 10,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 15,01</t>
+          <t>0,14; 15,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-41,05; 10,44</t>
+          <t>-41,33; 10,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 70,46</t>
+          <t>-21,84; 73,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-17,49; 67,14</t>
+          <t>-21,69; 73,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 206,43</t>
+          <t>-2,32; 211,72</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 8,26</t>
+          <t>-7,08; 8,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,99; 17,58</t>
+          <t>2,89; 16,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 14,22</t>
+          <t>0,3; 14,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 9,06</t>
+          <t>-2,0; 8,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 40,39</t>
+          <t>-26,59; 41,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,92; 159,79</t>
+          <t>14,42; 150,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 89,52</t>
+          <t>-1,05; 93,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,08; 173,8</t>
+          <t>-24,34; 159,46</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 5,31</t>
+          <t>-1,94; 5,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,6</t>
+          <t>0,93; 7,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,6; 8,27</t>
+          <t>1,64; 8,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 15,95</t>
+          <t>0,33; 17,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 24,81</t>
+          <t>-7,81; 25,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,25; 53,47</t>
+          <t>5,04; 52,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,06; 54,03</t>
+          <t>9,02; 58,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 101,24</t>
+          <t>0,54; 97,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP24_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP24_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 9,75</t>
+          <t>-14,44; 9,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 18,56</t>
+          <t>-7,63; 18,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 11,13</t>
+          <t>-10,68; 9,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 13,84</t>
+          <t>-14,01; 13,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-53,02; 62,28</t>
+          <t>-50,28; 58,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,03; 118,35</t>
+          <t>-29,24; 117,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-49,82; 125,08</t>
+          <t>-52,3; 108,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 22,19</t>
+          <t>-18,75; 21,38</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 17,7</t>
+          <t>1,59; 17,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 10,66</t>
+          <t>-7,63; 10,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 17,25</t>
+          <t>0,1; 17,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 53,86</t>
+          <t>2,06; 56,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 179,54</t>
+          <t>8,58; 193,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,55; 83,19</t>
+          <t>-34,87; 75,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 143,04</t>
+          <t>-3,13; 145,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,07; 654,7</t>
+          <t>9,0; 661,08</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 22,01</t>
+          <t>-1,76; 22,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 10,53</t>
+          <t>-9,94; 11,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 17,17</t>
+          <t>-5,22; 18,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 9,71</t>
+          <t>-8,59; 8,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 148,53</t>
+          <t>-7,89; 142,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-46,76; 101,19</t>
+          <t>-49,16; 111,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,22; 125,74</t>
+          <t>-23,9; 132,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-52,74; 144,99</t>
+          <t>-58,21; 133,73</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 11,92</t>
+          <t>-8,15; 11,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 15,22</t>
+          <t>-0,26; 14,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 21,68</t>
+          <t>-0,85; 21,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,91; 6,95</t>
+          <t>-38,17; 7,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,34; 95,86</t>
+          <t>-39,22; 90,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 416,54</t>
+          <t>-15,71; 478,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 172,97</t>
+          <t>-5,32; 163,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-82,62; 68,78</t>
+          <t>-82,53; 90,79</t>
         </is>
       </c>
     </row>
@@ -1060,37 +1060,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 22,99</t>
+          <t>-11,02; 21,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 14,52</t>
+          <t>-9,42; 14,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 9,21</t>
+          <t>-12,63; 9,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 0,0</t>
+          <t>-8,08; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 73,96</t>
+          <t>-22,8; 68,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-54,9; 165,56</t>
+          <t>-51,37; 168,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-78,82; 135,35</t>
+          <t>-71,05; 159,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 12,82</t>
+          <t>-12,09; 12,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,96; 9,51</t>
+          <t>-15,55; 8,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 8,93</t>
+          <t>-8,98; 8,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 9,17</t>
+          <t>-12,39; 9,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,51; 74,38</t>
+          <t>-43,04; 70,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-58,14; 88,76</t>
+          <t>-62,09; 71,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-65,97; 177,6</t>
+          <t>-61,3; 185,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,54; 66,62</t>
+          <t>-53,6; 66,34</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 2,76</t>
+          <t>-14,53; 5,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 11,11</t>
+          <t>-4,71; 11,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 10,72</t>
+          <t>-4,64; 11,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 15,71</t>
+          <t>-0,19; 14,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-41,33; 10,8</t>
+          <t>-40,91; 20,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-21,84; 73,51</t>
+          <t>-19,68; 76,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 73,66</t>
+          <t>-20,03; 72,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 211,72</t>
+          <t>-3,04; 204,34</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 8,27</t>
+          <t>-6,87; 9,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,89; 16,71</t>
+          <t>3,78; 17,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,3; 14,41</t>
+          <t>-0,21; 14,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 8,57</t>
+          <t>-2,44; 9,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,59; 41,18</t>
+          <t>-25,14; 45,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,42; 150,15</t>
+          <t>21,48; 157,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 93,95</t>
+          <t>0,4; 97,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-24,34; 159,46</t>
+          <t>-28,26; 180,44</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 5,5</t>
+          <t>-1,79; 5,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,64</t>
+          <t>0,89; 8,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,64; 8,55</t>
+          <t>1,71; 8,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,33; 17,93</t>
+          <t>-0,38; 15,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 25,93</t>
+          <t>-7,38; 26,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,04; 52,72</t>
+          <t>4,57; 57,12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,02; 58,78</t>
+          <t>8,73; 53,99</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,54; 97,65</t>
+          <t>-2,37; 94,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP24_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP24_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,47</t>
+          <t>-5,45</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-0,67%</t>
+          <t>-8,11%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 9,73</t>
+          <t>-15,02; 10,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 18,66</t>
+          <t>-9,03; 18,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 9,89</t>
+          <t>-10,42; 10,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 13,46</t>
+          <t>-18,5; 7,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-50,28; 58,75</t>
+          <t>-51,39; 70,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,24; 117,9</t>
+          <t>-33,51; 119,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-52,3; 108,42</t>
+          <t>-53,38; 120,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 21,38</t>
+          <t>-25,14; 13,78</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22,36</t>
+          <t>7,48</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>168,48%</t>
+          <t>58,4%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 17,87</t>
+          <t>1,51; 18,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 10,04</t>
+          <t>-6,65; 10,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 17,67</t>
+          <t>0,46; 18,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 56,83</t>
+          <t>-2,02; 16,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,58; 193,56</t>
+          <t>7,49; 187,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,87; 75,25</t>
+          <t>-31,49; 75,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 145,57</t>
+          <t>2,14; 149,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,0; 661,08</t>
+          <t>-14,66; 187,7</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 22,67</t>
+          <t>-1,95; 22,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 11,93</t>
+          <t>-9,13; 11,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 18,24</t>
+          <t>-5,69; 17,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 8,84</t>
+          <t>-6,62; 9,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 142,74</t>
+          <t>-8,87; 145,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,16; 111,59</t>
+          <t>-47,16; 115,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,9; 132,56</t>
+          <t>-25,4; 134,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-58,21; 133,73</t>
+          <t>-51,67; 154,23</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-8,6</t>
+          <t>-6,9</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-37,65%</t>
+          <t>-33,09%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 11,89</t>
+          <t>-8,39; 11,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 14,57</t>
+          <t>0,48; 15,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 21,33</t>
+          <t>-1,56; 22,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-38,17; 7,71</t>
+          <t>-39,09; 6,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,22; 90,72</t>
+          <t>-38,97; 92,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 478,11</t>
+          <t>-3,88; 431,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 163,96</t>
+          <t>-7,6; 182,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-82,53; 90,79</t>
+          <t>-80,39; 83,83</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,84</t>
+          <t>-2,19</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1060,37 +1060,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 21,7</t>
+          <t>-12,29; 23,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 14,59</t>
+          <t>-8,94; 15,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 9,26</t>
+          <t>-13,42; 9,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 0,0</t>
+          <t>-8,09; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-22,8; 68,86</t>
+          <t>-24,7; 74,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-51,37; 168,45</t>
+          <t>-47,73; 184,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-71,05; 159,82</t>
+          <t>-77,71; 140,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,94</t>
+          <t>-2,26</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-10,23%</t>
+          <t>-13,26%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 12,1</t>
+          <t>-13,48; 10,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,55; 8,81</t>
+          <t>-14,23; 9,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 8,9</t>
+          <t>-9,51; 9,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 9,73</t>
+          <t>-11,75; 8,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,04; 70,61</t>
+          <t>-44,27; 59,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-62,09; 71,78</t>
+          <t>-57,81; 88,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-61,3; 185,38</t>
+          <t>-66,69; 166,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,6; 66,34</t>
+          <t>-55,57; 68,72</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,01</t>
+          <t>5,59</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>50,85%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 5,23</t>
+          <t>-15,01; 2,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 11,56</t>
+          <t>-5,54; 10,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 11,36</t>
+          <t>-3,92; 10,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 14,4</t>
+          <t>-1,03; 13,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-40,91; 20,37</t>
+          <t>-41,05; 10,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,68; 76,42</t>
+          <t>-24,11; 70,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 72,97</t>
+          <t>-17,49; 67,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 204,34</t>
+          <t>-9,4; 170,06</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,22</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 9,11</t>
+          <t>-6,43; 8,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,78; 17,33</t>
+          <t>2,99; 17,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 14,57</t>
+          <t>-0,33; 14,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 9,05</t>
+          <t>-2,98; 7,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,14; 45,48</t>
+          <t>-23,53; 40,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,48; 157,46</t>
+          <t>15,92; 159,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 97,2</t>
+          <t>-2,75; 89,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,26; 180,44</t>
+          <t>-31,46; 155,59</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>1,32</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 5,75</t>
+          <t>-1,94; 5,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,03</t>
+          <t>1,23; 7,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,71; 8,43</t>
+          <t>1,6; 8,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 15,96</t>
+          <t>-2,87; 5,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 26,22</t>
+          <t>-7,92; 24,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,57; 57,12</t>
+          <t>7,25; 53,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,73; 53,99</t>
+          <t>9,06; 54,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 94,45</t>
+          <t>-15,86; 36,06</t>
         </is>
       </c>
     </row>
